--- a/DCF_Model_Asian_Paints.xlsx
+++ b/DCF_Model_Asian_Paints.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gayat\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E79BCB-5E6E-4487-896A-776D895214CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1E43C5-0415-4978-8FE7-356D18ED80BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF&gt;" sheetId="16" r:id="rId1"/>
@@ -32,12 +32,14 @@
     <sheet name="Referance" sheetId="25" r:id="rId17"/>
     <sheet name="DCF 1" sheetId="24" r:id="rId18"/>
     <sheet name="WACC(Arithmetic)" sheetId="20" r:id="rId19"/>
+    <sheet name="Comparable Valuation" sheetId="30" r:id="rId20"/>
+    <sheet name="DATA" sheetId="31" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Beta - Comps'!$P$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Common Size Statement'!$N$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'DCF 1'!$H$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">Forecasting!$U$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">Forecasting!$U$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Historical FS '!$O$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Intrisic Growth'!$I$73</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Ratio Analysis'!$P$33</definedName>
@@ -85,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="406">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -1284,6 +1286,144 @@
   <si>
     <t>Stock is overvalued</t>
   </si>
+  <si>
+    <t>Figures in crores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparable Company Valuation </t>
+  </si>
+  <si>
+    <t>Market Data</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Valuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company </t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share Price </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share Outstanding </t>
+  </si>
+  <si>
+    <t>Equtiy Value</t>
+  </si>
+  <si>
+    <t>Net Debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enterprise Value </t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>EV/Revenue</t>
+  </si>
+  <si>
+    <t>EV/EBITDA</t>
+  </si>
+  <si>
+    <t>P/E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S.No. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMP Rs. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Rs.Cr. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. Eq. Shares Cr. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt Rs.Cr. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Rs.Cr. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NP 12M Rs.Cr. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV / EBITDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kansai Nerolac </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSW Dulux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indigo Paints </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirca Paints </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shalimar Paints </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamdhenu Venture </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siddhika Coatins </t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>MA CAP</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>75th Percentile</t>
+  </si>
+  <si>
+    <t>25th Percentile</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Asian Paints Comparable Valuation</t>
+  </si>
+  <si>
+    <t>Implied Enterprise Value</t>
+  </si>
+  <si>
+    <t>Implied Market Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shares Outstanding </t>
+  </si>
+  <si>
+    <t>Implied Value per Share</t>
+  </si>
+  <si>
+    <t>Source: The Valuation School.in</t>
+  </si>
+  <si>
+    <t>Asian paints</t>
+  </si>
 </sst>
 </file>
 
@@ -1308,7 +1448,7 @@
     <numFmt numFmtId="178" formatCode="mmm\-yy&quot;E&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1458,6 +1598,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1520,7 +1681,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1666,6 +1827,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1680,7 +1850,7 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2009,11 +2179,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2042,12 +2216,56 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Accent6" xfId="3" builtinId="49"/>
@@ -2089,6 +2307,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14377</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1408981</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>88969</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCF7C267-5465-E37A-72BE-0AC0AB24B477}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a14:imgLayer r:embed="rId2">
+                  <a14:imgEffect>
+                    <a14:backgroundRemoval t="10000" b="90000" l="10000" r="90000"/>
+                  </a14:imgEffect>
+                </a14:imgLayer>
+              </a14:imgProps>
+            </a:ext>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="129397" y="194094"/>
+          <a:ext cx="1408980" cy="700007"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10614,11 +10896,11 @@
     </row>
     <row r="5" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16380" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="218" t="s">
+      <c r="B5" s="220" t="s">
         <v>347</v>
       </c>
-      <c r="C5" s="218"/>
-      <c r="D5" s="218"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="2"/>
       <c r="G5" s="2"/>
       <c r="J5" s="2"/>
@@ -18823,26 +19105,26 @@
       <c r="M6" s="71"/>
     </row>
     <row r="7" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16380" x14ac:dyDescent="0.3">
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="218" t="s">
         <v>339</v>
       </c>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="218"/>
       <c r="E7" s="71"/>
-      <c r="F7" s="217" t="s">
+      <c r="F7" s="219" t="s">
         <v>340</v>
       </c>
-      <c r="G7" s="217"/>
+      <c r="G7" s="219"/>
       <c r="H7" s="71"/>
-      <c r="I7" s="217" t="s">
+      <c r="I7" s="219" t="s">
         <v>342</v>
       </c>
-      <c r="J7" s="217"/>
+      <c r="J7" s="219"/>
       <c r="K7" s="71"/>
-      <c r="L7" s="217" t="s">
+      <c r="L7" s="219" t="s">
         <v>159</v>
       </c>
-      <c r="M7" s="217"/>
+      <c r="M7" s="219"/>
     </row>
     <row r="8" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16380" x14ac:dyDescent="0.3">
       <c r="B8" s="71"/>
@@ -21177,11 +21459,11 @@
       <c r="M76" s="81"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A77" s="216" t="s">
+      <c r="A77" s="218" t="s">
         <v>339</v>
       </c>
-      <c r="B77" s="216"/>
-      <c r="C77" s="216"/>
+      <c r="B77" s="218"/>
+      <c r="C77" s="218"/>
       <c r="D77" s="81"/>
       <c r="E77" s="71"/>
       <c r="F77" s="80"/>
@@ -21493,11 +21775,11 @@
       <c r="M97" s="81"/>
     </row>
     <row r="98" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B98" s="217" t="s">
+      <c r="B98" s="219" t="s">
         <v>340</v>
       </c>
-      <c r="C98" s="217"/>
-      <c r="D98" s="217"/>
+      <c r="C98" s="219"/>
+      <c r="D98" s="219"/>
       <c r="I98" s="76"/>
       <c r="J98" s="81"/>
       <c r="K98" s="71"/>
@@ -22085,10 +22367,10 @@
       <c r="M141" s="71"/>
     </row>
     <row r="142" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B142" s="217" t="s">
+      <c r="B142" s="219" t="s">
         <v>342</v>
       </c>
-      <c r="C142" s="217"/>
+      <c r="C142" s="219"/>
       <c r="K142" s="71"/>
       <c r="L142" s="71"/>
       <c r="M142" s="71"/>
@@ -22893,42 +23175,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="219" t="s">
+      <c r="B2" s="221" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="220"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="220"/>
-      <c r="J2" s="220"/>
-      <c r="K2" s="220"/>
+      <c r="C2" s="222"/>
+      <c r="D2" s="222"/>
+      <c r="E2" s="222"/>
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="220"/>
-      <c r="C3" s="220"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="220"/>
-      <c r="F3" s="220"/>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="220"/>
-      <c r="J3" s="220"/>
-      <c r="K3" s="220"/>
+      <c r="B3" s="222"/>
+      <c r="C3" s="222"/>
+      <c r="D3" s="222"/>
+      <c r="E3" s="222"/>
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
+      <c r="B4" s="222"/>
+      <c r="C4" s="222"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="168"/>
@@ -25583,16 +25865,16 @@
       <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="221" t="str">
+      <c r="E1" s="223" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
         <v/>
       </c>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -25601,15 +25883,15 @@
       <c r="B2" s="3">
         <v>2.1</v>
       </c>
-      <c r="E2" s="222" t="s">
+      <c r="E2" s="224" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="222"/>
-      <c r="G2" s="222"/>
-      <c r="H2" s="222"/>
-      <c r="I2" s="222"/>
-      <c r="J2" s="222"/>
-      <c r="K2" s="222"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="224"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -25660,10 +25942,17 @@
         <v>226872.36</v>
       </c>
     </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <f>B17- SUM(B18:B22)</f>
+        <v>5256.3099999999995</v>
+      </c>
+    </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="C15" s="16"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -29113,43 +29402,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B2" s="212" t="str">
+      <c r="B2" s="215" t="str">
         <f>"DCF Vatuation - "&amp;'Data Sheet'!B1</f>
         <v>DCF Vatuation - ASIAN PAINTS LTD</v>
       </c>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
     </row>
     <row r="3" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="212"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B4" s="212"/>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
@@ -29956,39 +30245,39 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="214" t="s">
+      <c r="B3" s="216" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="214"/>
-      <c r="D3" s="214"/>
-      <c r="E3" s="214"/>
-      <c r="F3" s="214"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="214"/>
-      <c r="I3" s="214"/>
-      <c r="J3" s="214"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="216"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
+      <c r="J3" s="216"/>
     </row>
     <row r="4" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="214"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="214"/>
-      <c r="E4" s="214"/>
-      <c r="F4" s="214"/>
-      <c r="G4" s="214"/>
-      <c r="H4" s="214"/>
-      <c r="I4" s="214"/>
-      <c r="J4" s="214"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
     </row>
     <row r="5" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="214"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="214"/>
-      <c r="E5" s="214"/>
-      <c r="F5" s="214"/>
-      <c r="G5" s="214"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="214"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="71"/>
@@ -30754,7 +31043,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B58F92E-028F-4F0C-8FCD-FCB4E5170C67}">
-  <dimension ref="B2:M52"/>
+  <dimension ref="B2:M47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.88671875" customWidth="1"/>
@@ -30770,46 +31059,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="212" t="str">
+      <c r="B2" s="215" t="str">
         <f>"DCF Vatuation - "&amp;'Data Sheet'!B1</f>
         <v>DCF Vatuation - ASIAN PAINTS LTD</v>
       </c>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="212"/>
-      <c r="L2" s="212"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="212"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
     </row>
     <row r="4" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="212"/>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
+      <c r="L4" s="215"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
@@ -31214,14 +31503,14 @@
       <c r="C31" s="61"/>
       <c r="D31" s="61"/>
       <c r="E31" s="61"/>
-      <c r="G31" s="213" t="s">
+      <c r="G31" s="214" t="s">
         <v>334</v>
       </c>
-      <c r="H31" s="213"/>
-      <c r="I31" s="213"/>
-      <c r="J31" s="213"/>
-      <c r="K31" s="213"/>
-      <c r="L31" s="213"/>
+      <c r="H31" s="214"/>
+      <c r="I31" s="214"/>
+      <c r="J31" s="214"/>
+      <c r="K31" s="214"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="198"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
@@ -31306,7 +31595,7 @@
       <c r="J35" s="198">
         <v>106614.98800165884</v>
       </c>
-      <c r="K35" s="223">
+      <c r="K35" s="212">
         <v>101386.92351285199</v>
       </c>
       <c r="L35" s="198">
@@ -31481,18 +31770,15 @@
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B47" s="225" t="s">
+      <c r="B47" s="157" t="s">
         <v>359</v>
       </c>
-      <c r="C47" s="225"/>
-      <c r="D47" s="225"/>
-      <c r="E47" s="226">
+      <c r="C47" s="157"/>
+      <c r="D47" s="157"/>
+      <c r="E47" s="213">
         <f>(E44-E42)/E42</f>
         <v>1.0906257556123107</v>
       </c>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E52" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -31504,6 +31790,1584 @@
   <ignoredErrors>
     <ignoredError sqref="E38" formulaRange="1"/>
   </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7556F5-D5F3-4CC6-9FFF-EA0708DADEB4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:Q40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" customWidth="1"/>
+    <col min="10" max="10" width="1.88671875" customWidth="1"/>
+    <col min="11" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" customWidth="1"/>
+    <col min="14" max="14" width="1.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.5546875" customWidth="1"/>
+    <col min="16" max="16" width="12.77734375" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="194"/>
+      <c r="C2" s="194"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="194"/>
+      <c r="G2" s="194"/>
+      <c r="H2" s="194"/>
+      <c r="I2" s="194"/>
+      <c r="J2" s="194"/>
+      <c r="K2" s="194"/>
+      <c r="L2" s="194"/>
+      <c r="M2" s="194"/>
+      <c r="N2" s="194"/>
+      <c r="O2" s="194"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+    </row>
+    <row r="3" spans="2:17" ht="21" x14ac:dyDescent="0.4">
+      <c r="B3" s="225"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+    </row>
+    <row r="4" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="226" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+    </row>
+    <row r="5" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="226"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="85" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="60" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="228"/>
+      <c r="J8" s="228"/>
+      <c r="K8" s="228"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="229" t="s">
+        <v>362</v>
+      </c>
+      <c r="E10" s="230"/>
+      <c r="F10" s="230"/>
+      <c r="G10" s="230"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="230"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="229" t="s">
+        <v>363</v>
+      </c>
+      <c r="L10" s="229"/>
+      <c r="M10" s="229"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="229" t="s">
+        <v>364</v>
+      </c>
+      <c r="P10" s="230"/>
+      <c r="Q10" s="230"/>
+    </row>
+    <row r="11" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="D11" s="231" t="s">
+        <v>367</v>
+      </c>
+      <c r="E11" s="231" t="s">
+        <v>368</v>
+      </c>
+      <c r="F11" s="231" t="s">
+        <v>369</v>
+      </c>
+      <c r="G11" s="232" t="s">
+        <v>370</v>
+      </c>
+      <c r="H11" s="231" t="s">
+        <v>371</v>
+      </c>
+      <c r="I11" s="232"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="232" t="s">
+        <v>372</v>
+      </c>
+      <c r="L11" s="232" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="232" t="s">
+        <v>373</v>
+      </c>
+      <c r="N11" s="232"/>
+      <c r="O11" s="232" t="s">
+        <v>374</v>
+      </c>
+      <c r="P11" s="232" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q11" s="232" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="199"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="199"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="199"/>
+      <c r="K12" s="199"/>
+      <c r="L12" s="199"/>
+      <c r="M12" s="199"/>
+      <c r="N12" s="199"/>
+      <c r="O12" s="199"/>
+      <c r="P12" s="199"/>
+      <c r="Q12" s="199"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="234" t="str">
+        <f>DATA!B4</f>
+        <v xml:space="preserve">Asian Paints </v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="237">
+        <f>DATA!C4</f>
+        <v>2485.1</v>
+      </c>
+      <c r="E13" s="239">
+        <f>DATA!D4</f>
+        <v>95.92</v>
+      </c>
+      <c r="F13" s="237">
+        <f>D13*E13</f>
+        <v>238370.79199999999</v>
+      </c>
+      <c r="G13" s="237">
+        <f>DATA!F4-DATA!H4</f>
+        <v>2546.42</v>
+      </c>
+      <c r="H13" s="237">
+        <f>DATA!K4</f>
+        <v>240917.21199999997</v>
+      </c>
+      <c r="I13" s="237"/>
+      <c r="J13" s="237"/>
+      <c r="K13" s="237">
+        <f>DATA!G4</f>
+        <v>34695.75</v>
+      </c>
+      <c r="L13" s="237">
+        <f>DATA!L4</f>
+        <v>7163.7589057389223</v>
+      </c>
+      <c r="M13" s="237">
+        <f>DATA!I4</f>
+        <v>3910.03</v>
+      </c>
+      <c r="N13" s="237"/>
+      <c r="O13" s="241">
+        <f>H13/K13</f>
+        <v>6.943709589791256</v>
+      </c>
+      <c r="P13" s="241">
+        <f>H13/L13</f>
+        <v>33.630000000000003</v>
+      </c>
+      <c r="Q13" s="241">
+        <f>F13/M13</f>
+        <v>60.963929177013981</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="235" t="str">
+        <f>DATA!B5</f>
+        <v xml:space="preserve">Berger Paints </v>
+      </c>
+      <c r="C14" s="235"/>
+      <c r="D14" s="238">
+        <f>DATA!C5</f>
+        <v>460.4</v>
+      </c>
+      <c r="E14" s="240">
+        <f>DATA!D5</f>
+        <v>116.6</v>
+      </c>
+      <c r="F14" s="238">
+        <f t="shared" ref="F14:F21" si="0">D14*E14</f>
+        <v>53682.639999999992</v>
+      </c>
+      <c r="G14" s="238">
+        <f>DATA!F5-DATA!H5</f>
+        <v>247.50000000000006</v>
+      </c>
+      <c r="H14" s="238">
+        <f>DATA!K5</f>
+        <v>53930.139999999992</v>
+      </c>
+      <c r="I14" s="238"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="238">
+        <f>DATA!G5</f>
+        <v>11716.25</v>
+      </c>
+      <c r="L14" s="238">
+        <f>DATA!L5</f>
+        <v>1930.2125984251966</v>
+      </c>
+      <c r="M14" s="238">
+        <f>DATA!I5</f>
+        <v>1055.68</v>
+      </c>
+      <c r="N14" s="238"/>
+      <c r="O14" s="242">
+        <f t="shared" ref="O14:O21" si="1">H14/K14</f>
+        <v>4.6030205910594253</v>
+      </c>
+      <c r="P14" s="242">
+        <f t="shared" ref="P14:P21" si="2">H14/L14</f>
+        <v>27.94</v>
+      </c>
+      <c r="Q14" s="242">
+        <f t="shared" ref="Q14:Q21" si="3">F14/M14</f>
+        <v>50.85124280084873</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B15" s="235" t="str">
+        <f>DATA!B6</f>
+        <v xml:space="preserve">Kansai Nerolac </v>
+      </c>
+      <c r="C15" s="235"/>
+      <c r="D15" s="238">
+        <f>DATA!C6</f>
+        <v>197.15</v>
+      </c>
+      <c r="E15" s="240">
+        <f>DATA!D6</f>
+        <v>80.87</v>
+      </c>
+      <c r="F15" s="238">
+        <f t="shared" si="0"/>
+        <v>15943.520500000001</v>
+      </c>
+      <c r="G15" s="238">
+        <f>DATA!F6-DATA!H6</f>
+        <v>9.1100000000000136</v>
+      </c>
+      <c r="H15" s="238">
+        <f>DATA!K6</f>
+        <v>15952.630500000001</v>
+      </c>
+      <c r="I15" s="238"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="238">
+        <f>DATA!G6</f>
+        <v>7914.85</v>
+      </c>
+      <c r="L15" s="238">
+        <f>DATA!L6</f>
+        <v>1076.4258097165991</v>
+      </c>
+      <c r="M15" s="238">
+        <f>DATA!I6</f>
+        <v>568.38</v>
+      </c>
+      <c r="N15" s="238"/>
+      <c r="O15" s="242">
+        <f t="shared" si="1"/>
+        <v>2.0155316272576234</v>
+      </c>
+      <c r="P15" s="242">
+        <f t="shared" si="2"/>
+        <v>14.820000000000002</v>
+      </c>
+      <c r="Q15" s="242">
+        <f t="shared" si="3"/>
+        <v>28.050811956789474</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B16" s="235" t="str">
+        <f>DATA!B7</f>
+        <v xml:space="preserve">JSW Dulux </v>
+      </c>
+      <c r="C16" s="235"/>
+      <c r="D16" s="238">
+        <f>DATA!C7</f>
+        <v>2947.8</v>
+      </c>
+      <c r="E16" s="240">
+        <f>DATA!D7</f>
+        <v>4.55</v>
+      </c>
+      <c r="F16" s="238">
+        <f t="shared" si="0"/>
+        <v>13412.49</v>
+      </c>
+      <c r="G16" s="238">
+        <f>DATA!F7-DATA!H7</f>
+        <v>-202.8</v>
+      </c>
+      <c r="H16" s="238">
+        <f>DATA!K7</f>
+        <v>13209.69</v>
+      </c>
+      <c r="I16" s="238"/>
+      <c r="J16" s="238"/>
+      <c r="K16" s="238">
+        <f>DATA!G7</f>
+        <v>3759.8</v>
+      </c>
+      <c r="L16" s="238">
+        <f>DATA!L7</f>
+        <v>574.0847457627118</v>
+      </c>
+      <c r="M16" s="238">
+        <f>DATA!I7</f>
+        <v>1955.3</v>
+      </c>
+      <c r="N16" s="238"/>
+      <c r="O16" s="242">
+        <f t="shared" si="1"/>
+        <v>3.5134023086334381</v>
+      </c>
+      <c r="P16" s="242">
+        <f t="shared" si="2"/>
+        <v>23.01</v>
+      </c>
+      <c r="Q16" s="242">
+        <f t="shared" si="3"/>
+        <v>6.8595560783511482</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17" s="235" t="str">
+        <f>DATA!B8</f>
+        <v xml:space="preserve">Indigo Paints </v>
+      </c>
+      <c r="C17" s="235"/>
+      <c r="D17" s="238">
+        <f>DATA!C8</f>
+        <v>860.05</v>
+      </c>
+      <c r="E17" s="240">
+        <f>DATA!D8</f>
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F17" s="238">
+        <f t="shared" si="0"/>
+        <v>4102.4384999999993</v>
+      </c>
+      <c r="G17" s="238">
+        <f>DATA!F8-DATA!H8</f>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="H17" s="238">
+        <f>DATA!K8</f>
+        <v>4110.9884999999995</v>
+      </c>
+      <c r="I17" s="238"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="238">
+        <f>DATA!G8</f>
+        <v>1299.42</v>
+      </c>
+      <c r="L17" s="238">
+        <f>DATA!L8</f>
+        <v>259.04149338374287</v>
+      </c>
+      <c r="M17" s="238">
+        <f>DATA!I8</f>
+        <v>144.94999999999999</v>
+      </c>
+      <c r="N17" s="238"/>
+      <c r="O17" s="242">
+        <f t="shared" si="1"/>
+        <v>3.1637103476935859</v>
+      </c>
+      <c r="P17" s="242">
+        <f t="shared" si="2"/>
+        <v>15.870000000000001</v>
+      </c>
+      <c r="Q17" s="242">
+        <f t="shared" si="3"/>
+        <v>28.302438771990339</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18" s="235" t="str">
+        <f>DATA!B9</f>
+        <v xml:space="preserve">Sirca Paints </v>
+      </c>
+      <c r="C18" s="235"/>
+      <c r="D18" s="238">
+        <f>DATA!C9</f>
+        <v>437.3</v>
+      </c>
+      <c r="E18" s="240">
+        <f>DATA!D9</f>
+        <v>5.68</v>
+      </c>
+      <c r="F18" s="238">
+        <f t="shared" si="0"/>
+        <v>2483.864</v>
+      </c>
+      <c r="G18" s="238">
+        <f>DATA!F9-DATA!H9</f>
+        <v>-7.6200000000000045</v>
+      </c>
+      <c r="H18" s="238">
+        <f>DATA!K9</f>
+        <v>2476.2439999999997</v>
+      </c>
+      <c r="I18" s="238"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="238">
+        <f>DATA!G9</f>
+        <v>459.12</v>
+      </c>
+      <c r="L18" s="238">
+        <f>DATA!L9</f>
+        <v>95.570976456966406</v>
+      </c>
+      <c r="M18" s="238">
+        <f>DATA!I9</f>
+        <v>61.5</v>
+      </c>
+      <c r="N18" s="238"/>
+      <c r="O18" s="242">
+        <f t="shared" si="1"/>
+        <v>5.3934570482662476</v>
+      </c>
+      <c r="P18" s="242">
+        <f t="shared" si="2"/>
+        <v>25.91</v>
+      </c>
+      <c r="Q18" s="242">
+        <f t="shared" si="3"/>
+        <v>40.388032520325204</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19" s="235" t="str">
+        <f>DATA!B10</f>
+        <v xml:space="preserve">Shalimar Paints </v>
+      </c>
+      <c r="C19" s="235"/>
+      <c r="D19" s="238">
+        <f>DATA!C10</f>
+        <v>50.1</v>
+      </c>
+      <c r="E19" s="240">
+        <f>DATA!D10</f>
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="F19" s="238">
+        <f t="shared" si="0"/>
+        <v>419.33699999999999</v>
+      </c>
+      <c r="G19" s="238">
+        <f>DATA!F10-DATA!H10</f>
+        <v>141.53</v>
+      </c>
+      <c r="H19" s="238">
+        <f>DATA!K10</f>
+        <v>560.86699999999996</v>
+      </c>
+      <c r="I19" s="238"/>
+      <c r="J19" s="238"/>
+      <c r="K19" s="238">
+        <f>DATA!G10</f>
+        <v>597.53</v>
+      </c>
+      <c r="L19" s="238">
+        <f>DATA!L10</f>
+        <v>-19.413880235375562</v>
+      </c>
+      <c r="M19" s="238">
+        <f>DATA!I10</f>
+        <v>-67.08</v>
+      </c>
+      <c r="N19" s="238"/>
+      <c r="O19" s="242">
+        <f t="shared" si="1"/>
+        <v>0.93864241125968573</v>
+      </c>
+      <c r="P19" s="242">
+        <f t="shared" si="2"/>
+        <v>-28.89</v>
+      </c>
+      <c r="Q19" s="242">
+        <f t="shared" si="3"/>
+        <v>-6.2512969588550984</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="235" t="str">
+        <f>DATA!B11</f>
+        <v xml:space="preserve">Kamdhenu Venture </v>
+      </c>
+      <c r="C20" s="235"/>
+      <c r="D20" s="238">
+        <f>DATA!C11</f>
+        <v>5.62</v>
+      </c>
+      <c r="E20" s="240">
+        <f>DATA!D11</f>
+        <v>32.9</v>
+      </c>
+      <c r="F20" s="238">
+        <f t="shared" si="0"/>
+        <v>184.898</v>
+      </c>
+      <c r="G20" s="238">
+        <f>DATA!F11-DATA!H11</f>
+        <v>25.47</v>
+      </c>
+      <c r="H20" s="238">
+        <f>DATA!K11</f>
+        <v>210.36799999999999</v>
+      </c>
+      <c r="I20" s="238"/>
+      <c r="J20" s="238"/>
+      <c r="K20" s="238">
+        <f>DATA!G11</f>
+        <v>253.02</v>
+      </c>
+      <c r="L20" s="238">
+        <f>DATA!L11</f>
+        <v>16.244633204633207</v>
+      </c>
+      <c r="M20" s="238">
+        <f>DATA!I11</f>
+        <v>4.76</v>
+      </c>
+      <c r="N20" s="238"/>
+      <c r="O20" s="242">
+        <f t="shared" si="1"/>
+        <v>0.83142834558532919</v>
+      </c>
+      <c r="P20" s="242">
+        <f t="shared" si="2"/>
+        <v>12.949999999999998</v>
+      </c>
+      <c r="Q20" s="242">
+        <f t="shared" si="3"/>
+        <v>38.844117647058823</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B21" s="235" t="str">
+        <f>DATA!B12</f>
+        <v xml:space="preserve">Siddhika Coatins </v>
+      </c>
+      <c r="C21" s="235"/>
+      <c r="D21" s="238">
+        <f>DATA!C12</f>
+        <v>221.95</v>
+      </c>
+      <c r="E21" s="240">
+        <f>DATA!D12</f>
+        <v>0.62</v>
+      </c>
+      <c r="F21" s="238">
+        <f t="shared" si="0"/>
+        <v>137.60899999999998</v>
+      </c>
+      <c r="G21" s="238">
+        <f>DATA!F12-DATA!H12</f>
+        <v>-5.9</v>
+      </c>
+      <c r="H21" s="238">
+        <f>DATA!K12</f>
+        <v>131.70899999999997</v>
+      </c>
+      <c r="I21" s="238"/>
+      <c r="J21" s="238"/>
+      <c r="K21" s="238">
+        <f>DATA!G12</f>
+        <v>51.6</v>
+      </c>
+      <c r="L21" s="238">
+        <f>DATA!L12</f>
+        <v>11.854995499549954</v>
+      </c>
+      <c r="M21" s="238">
+        <f>DATA!I12</f>
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="N21" s="238"/>
+      <c r="O21" s="242">
+        <f t="shared" si="1"/>
+        <v>2.5524999999999993</v>
+      </c>
+      <c r="P21" s="242">
+        <f t="shared" si="2"/>
+        <v>11.11</v>
+      </c>
+      <c r="Q21" s="242">
+        <f t="shared" si="3"/>
+        <v>16.113466042154567</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="233"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="234" t="s">
+        <v>395</v>
+      </c>
+      <c r="C23" s="234"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="234"/>
+      <c r="G23" s="234"/>
+      <c r="H23" s="234"/>
+      <c r="I23" s="234"/>
+      <c r="J23" s="234"/>
+      <c r="K23" s="234"/>
+      <c r="L23" s="234"/>
+      <c r="M23" s="234"/>
+      <c r="N23" s="234"/>
+      <c r="O23" s="243">
+        <f>MAX(O13:O21)</f>
+        <v>6.943709589791256</v>
+      </c>
+      <c r="P23" s="243">
+        <f t="shared" ref="P23:Q23" si="4">MAX(P13:P21)</f>
+        <v>33.630000000000003</v>
+      </c>
+      <c r="Q23" s="243">
+        <f t="shared" si="4"/>
+        <v>60.963929177013981</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="234" t="s">
+        <v>396</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="234"/>
+      <c r="I24" s="234"/>
+      <c r="J24" s="234"/>
+      <c r="K24" s="234"/>
+      <c r="L24" s="234"/>
+      <c r="M24" s="234"/>
+      <c r="N24" s="234"/>
+      <c r="O24" s="243">
+        <f>QUARTILE(O13:O21,3)</f>
+        <v>4.6030205910594253</v>
+      </c>
+      <c r="P24" s="243">
+        <f t="shared" ref="P24:Q24" si="5">QUARTILE(P13:P21,3)</f>
+        <v>25.91</v>
+      </c>
+      <c r="Q24" s="243">
+        <f t="shared" si="5"/>
+        <v>40.388032520325204</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B25" s="236" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" s="236"/>
+      <c r="D25" s="236"/>
+      <c r="E25" s="236"/>
+      <c r="F25" s="236"/>
+      <c r="G25" s="236"/>
+      <c r="H25" s="236"/>
+      <c r="I25" s="236"/>
+      <c r="J25" s="236"/>
+      <c r="K25" s="236"/>
+      <c r="L25" s="236"/>
+      <c r="M25" s="236"/>
+      <c r="N25" s="236"/>
+      <c r="O25" s="244">
+        <f>AVERAGE(O13:O21)</f>
+        <v>3.3283780299496213</v>
+      </c>
+      <c r="P25" s="244">
+        <f t="shared" ref="P25:Q25" si="6">AVERAGE(P13:P21)</f>
+        <v>15.150000000000002</v>
+      </c>
+      <c r="Q25" s="244">
+        <f t="shared" si="6"/>
+        <v>29.346922003964135</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B26" s="236" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" s="236"/>
+      <c r="D26" s="236"/>
+      <c r="E26" s="236"/>
+      <c r="F26" s="236"/>
+      <c r="G26" s="236"/>
+      <c r="H26" s="236"/>
+      <c r="I26" s="236"/>
+      <c r="J26" s="236"/>
+      <c r="K26" s="236"/>
+      <c r="L26" s="236"/>
+      <c r="M26" s="236"/>
+      <c r="N26" s="236"/>
+      <c r="O26" s="244">
+        <f>MEDIAN(O13:O21)</f>
+        <v>3.1637103476935859</v>
+      </c>
+      <c r="P26" s="244">
+        <f t="shared" ref="P26:Q26" si="7">MEDIAN(P13:P21)</f>
+        <v>15.870000000000001</v>
+      </c>
+      <c r="Q26" s="244">
+        <f t="shared" si="7"/>
+        <v>28.302438771990339</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="234" t="s">
+        <v>397</v>
+      </c>
+      <c r="C27" s="234"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="234"/>
+      <c r="G27" s="234"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="234"/>
+      <c r="J27" s="234"/>
+      <c r="K27" s="234"/>
+      <c r="L27" s="234"/>
+      <c r="M27" s="234"/>
+      <c r="N27" s="234"/>
+      <c r="O27" s="243">
+        <f>QUARTILE(O13:O21,1)</f>
+        <v>2.0155316272576234</v>
+      </c>
+      <c r="P27" s="243">
+        <f t="shared" ref="P27:Q27" si="8">QUARTILE(P13:P21,1)</f>
+        <v>12.949999999999998</v>
+      </c>
+      <c r="Q27" s="243">
+        <f t="shared" si="8"/>
+        <v>16.113466042154567</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="234" t="s">
+        <v>398</v>
+      </c>
+      <c r="C28" s="234"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="234"/>
+      <c r="F28" s="234"/>
+      <c r="G28" s="234"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="234"/>
+      <c r="J28" s="234"/>
+      <c r="K28" s="234"/>
+      <c r="L28" s="234"/>
+      <c r="M28" s="234"/>
+      <c r="N28" s="234"/>
+      <c r="O28" s="243">
+        <f>MIN(O13:O21)</f>
+        <v>0.83142834558532919</v>
+      </c>
+      <c r="P28" s="243">
+        <f t="shared" ref="P28:Q28" si="9">MIN(P13:P21)</f>
+        <v>-28.89</v>
+      </c>
+      <c r="Q28" s="243">
+        <f t="shared" si="9"/>
+        <v>-6.2512969588550984</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B30" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="232" t="s">
+        <v>374</v>
+      </c>
+      <c r="P30" s="232" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q30" s="232" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B32" s="235" t="s">
+        <v>400</v>
+      </c>
+      <c r="C32" s="235"/>
+      <c r="D32" s="235"/>
+      <c r="E32" s="235"/>
+      <c r="F32" s="235"/>
+      <c r="G32" s="235"/>
+      <c r="H32" s="235"/>
+      <c r="I32" s="235"/>
+      <c r="J32" s="235"/>
+      <c r="K32" s="235"/>
+      <c r="L32" s="235"/>
+      <c r="M32" s="235"/>
+      <c r="N32" s="235"/>
+      <c r="O32" s="237">
+        <f>O$26*K13</f>
+        <v>109767.30329598974</v>
+      </c>
+      <c r="P32" s="237">
+        <f>P$26*L13</f>
+        <v>113688.8538340767</v>
+      </c>
+      <c r="Q32" s="247">
+        <f>+Q33+Q34</f>
+        <v>113209.80467164538</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B33" s="235" t="s">
+        <v>370</v>
+      </c>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
+      <c r="I33" s="235"/>
+      <c r="J33" s="235"/>
+      <c r="K33" s="235"/>
+      <c r="L33" s="235"/>
+      <c r="M33" s="235"/>
+      <c r="N33" s="235"/>
+      <c r="O33" s="247">
+        <f>$G$13</f>
+        <v>2546.42</v>
+      </c>
+      <c r="P33" s="247">
+        <f t="shared" ref="P33:Q33" si="10">$G$13</f>
+        <v>2546.42</v>
+      </c>
+      <c r="Q33" s="247">
+        <f t="shared" si="10"/>
+        <v>2546.42</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B34" s="235" t="s">
+        <v>401</v>
+      </c>
+      <c r="C34" s="235"/>
+      <c r="D34" s="235"/>
+      <c r="E34" s="235"/>
+      <c r="F34" s="235"/>
+      <c r="G34" s="235"/>
+      <c r="H34" s="235"/>
+      <c r="I34" s="235"/>
+      <c r="J34" s="235"/>
+      <c r="K34" s="235"/>
+      <c r="L34" s="235"/>
+      <c r="M34" s="235"/>
+      <c r="N34" s="235"/>
+      <c r="O34" s="247">
+        <f>O32-O33</f>
+        <v>107220.88329598974</v>
+      </c>
+      <c r="P34" s="247">
+        <f t="shared" ref="P34" si="11">P32-P33</f>
+        <v>111142.4338340767</v>
+      </c>
+      <c r="Q34" s="235">
+        <f>M13*Q26</f>
+        <v>110663.38467164538</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B35" s="235" t="s">
+        <v>402</v>
+      </c>
+      <c r="C35" s="235"/>
+      <c r="D35" s="235"/>
+      <c r="E35" s="235"/>
+      <c r="F35" s="235"/>
+      <c r="G35" s="235"/>
+      <c r="H35" s="235"/>
+      <c r="I35" s="235"/>
+      <c r="J35" s="235"/>
+      <c r="K35" s="235"/>
+      <c r="L35" s="235"/>
+      <c r="M35" s="235"/>
+      <c r="N35" s="235"/>
+      <c r="O35" s="235">
+        <f>$E$13</f>
+        <v>95.92</v>
+      </c>
+      <c r="P35" s="235">
+        <f t="shared" ref="P35:Q35" si="12">$E$13</f>
+        <v>95.92</v>
+      </c>
+      <c r="Q35" s="235">
+        <f t="shared" si="12"/>
+        <v>95.92</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" ht="3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
+      <c r="J36" s="245"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="245"/>
+      <c r="M36" s="245"/>
+      <c r="N36" s="245"/>
+      <c r="O36" s="245"/>
+      <c r="P36" s="245"/>
+      <c r="Q36" s="245"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B37" s="246" t="s">
+        <v>403</v>
+      </c>
+      <c r="C37" s="246"/>
+      <c r="D37" s="246"/>
+      <c r="E37" s="246"/>
+      <c r="F37" s="246"/>
+      <c r="G37" s="246"/>
+      <c r="H37" s="246"/>
+      <c r="I37" s="246"/>
+      <c r="J37" s="246"/>
+      <c r="K37" s="246"/>
+      <c r="L37" s="246"/>
+      <c r="M37" s="246"/>
+      <c r="N37" s="246"/>
+      <c r="O37" s="248">
+        <f>O34/O35</f>
+        <v>1117.8157140949722</v>
+      </c>
+      <c r="P37" s="248">
+        <f>P34/P35</f>
+        <v>1158.6992684953784</v>
+      </c>
+      <c r="Q37" s="248">
+        <f>Q34/Q35</f>
+        <v>1153.7050111722829</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B39" s="85" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O40" t="str">
+        <f>IF(O37&gt;$D$13,"Undervalued","Overvalued")</f>
+        <v>Overvalued</v>
+      </c>
+      <c r="P40" t="str">
+        <f>IF(P37&gt;$D$13,"Undervalued","Overvalued")</f>
+        <v>Overvalued</v>
+      </c>
+      <c r="Q40" t="str">
+        <f>IF(Q37&gt;$D$13,"Undervalued","Overvalued")</f>
+        <v>Overvalued</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="O10:Q10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5025B8F4-2BCE-415D-B83C-728D89856F71}">
+  <dimension ref="A3:L12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F3" t="s">
+        <v>382</v>
+      </c>
+      <c r="G3" t="s">
+        <v>380</v>
+      </c>
+      <c r="H3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I3" t="s">
+        <v>384</v>
+      </c>
+      <c r="J3" t="s">
+        <v>385</v>
+      </c>
+      <c r="K3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4">
+        <v>2485.1</v>
+      </c>
+      <c r="D4">
+        <v>95.92</v>
+      </c>
+      <c r="E4">
+        <f>C4*D4</f>
+        <v>238370.79199999999</v>
+      </c>
+      <c r="F4">
+        <v>3557.09</v>
+      </c>
+      <c r="G4">
+        <v>34695.75</v>
+      </c>
+      <c r="H4">
+        <v>1010.67</v>
+      </c>
+      <c r="I4">
+        <v>3910.03</v>
+      </c>
+      <c r="J4">
+        <v>33.630000000000003</v>
+      </c>
+      <c r="K4">
+        <f>E4+F4-H4</f>
+        <v>240917.21199999997</v>
+      </c>
+      <c r="L4">
+        <f>K4/J4</f>
+        <v>7163.7589057389223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5">
+        <v>460.4</v>
+      </c>
+      <c r="D5">
+        <v>116.6</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E12" si="0">C5*D5</f>
+        <v>53682.639999999992</v>
+      </c>
+      <c r="F5">
+        <v>697.33</v>
+      </c>
+      <c r="G5">
+        <v>11716.25</v>
+      </c>
+      <c r="H5">
+        <v>449.83</v>
+      </c>
+      <c r="I5">
+        <v>1055.68</v>
+      </c>
+      <c r="J5">
+        <v>27.94</v>
+      </c>
+      <c r="K5">
+        <f>E5+F5-H5</f>
+        <v>53930.139999999992</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L12" si="1">K5/J5</f>
+        <v>1930.2125984251966</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C6">
+        <v>197.15</v>
+      </c>
+      <c r="D6">
+        <v>80.87</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>15943.520500000001</v>
+      </c>
+      <c r="F6">
+        <v>276.42</v>
+      </c>
+      <c r="G6">
+        <v>7914.85</v>
+      </c>
+      <c r="H6">
+        <v>267.31</v>
+      </c>
+      <c r="I6">
+        <v>568.38</v>
+      </c>
+      <c r="J6">
+        <v>14.82</v>
+      </c>
+      <c r="K6">
+        <f>E6+F6-H6</f>
+        <v>15952.630500000001</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>1076.4258097165991</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7">
+        <v>2947.8</v>
+      </c>
+      <c r="D7">
+        <v>4.55</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>13412.49</v>
+      </c>
+      <c r="F7">
+        <v>71.2</v>
+      </c>
+      <c r="G7">
+        <v>3759.8</v>
+      </c>
+      <c r="H7">
+        <v>274</v>
+      </c>
+      <c r="I7">
+        <v>1955.3</v>
+      </c>
+      <c r="J7">
+        <v>23.01</v>
+      </c>
+      <c r="K7">
+        <f>E7+F7-H7</f>
+        <v>13209.69</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="1"/>
+        <v>574.0847457627118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C8">
+        <v>860.05</v>
+      </c>
+      <c r="D8">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>4102.4384999999993</v>
+      </c>
+      <c r="F8">
+        <v>17.64</v>
+      </c>
+      <c r="G8">
+        <v>1299.42</v>
+      </c>
+      <c r="H8">
+        <v>9.09</v>
+      </c>
+      <c r="I8">
+        <v>144.94999999999999</v>
+      </c>
+      <c r="J8">
+        <v>15.87</v>
+      </c>
+      <c r="K8">
+        <f>E8+F8-H8</f>
+        <v>4110.9884999999995</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>259.04149338374287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C9">
+        <v>437.3</v>
+      </c>
+      <c r="D9">
+        <v>5.68</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>2483.864</v>
+      </c>
+      <c r="F9">
+        <v>45.22</v>
+      </c>
+      <c r="G9">
+        <v>459.12</v>
+      </c>
+      <c r="H9">
+        <v>52.84</v>
+      </c>
+      <c r="I9">
+        <v>61.5</v>
+      </c>
+      <c r="J9">
+        <v>25.91</v>
+      </c>
+      <c r="K9">
+        <f>E9+F9-H9</f>
+        <v>2476.2439999999997</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>95.570976456966406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10">
+        <v>50.1</v>
+      </c>
+      <c r="D10">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>419.33699999999999</v>
+      </c>
+      <c r="F10">
+        <v>189.6</v>
+      </c>
+      <c r="G10">
+        <v>597.53</v>
+      </c>
+      <c r="H10">
+        <v>48.07</v>
+      </c>
+      <c r="I10">
+        <v>-67.08</v>
+      </c>
+      <c r="J10">
+        <v>-28.89</v>
+      </c>
+      <c r="K10">
+        <f>E10+F10-H10</f>
+        <v>560.86699999999996</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>-19.413880235375562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>391</v>
+      </c>
+      <c r="C11">
+        <v>5.62</v>
+      </c>
+      <c r="D11">
+        <v>32.9</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>184.898</v>
+      </c>
+      <c r="F11">
+        <v>32.229999999999997</v>
+      </c>
+      <c r="G11">
+        <v>253.02</v>
+      </c>
+      <c r="H11">
+        <v>6.76</v>
+      </c>
+      <c r="I11">
+        <v>4.76</v>
+      </c>
+      <c r="J11">
+        <v>12.95</v>
+      </c>
+      <c r="K11">
+        <f>E11+F11-H11</f>
+        <v>210.36799999999999</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>16.244633204633207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C12">
+        <v>221.95</v>
+      </c>
+      <c r="D12">
+        <v>0.62</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>137.60899999999998</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>51.6</v>
+      </c>
+      <c r="H12">
+        <v>5.9</v>
+      </c>
+      <c r="I12">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="J12">
+        <v>11.11</v>
+      </c>
+      <c r="K12">
+        <f>E12+F12-H12</f>
+        <v>131.70899999999997</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>11.854995499549954</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -31525,39 +33389,39 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="216" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="214"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="214"/>
-      <c r="I2" s="214"/>
-      <c r="J2" s="214"/>
+      <c r="C2" s="216"/>
+      <c r="D2" s="216"/>
+      <c r="E2" s="216"/>
+      <c r="F2" s="216"/>
+      <c r="G2" s="216"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="216"/>
+      <c r="J2" s="216"/>
     </row>
     <row r="3" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="214"/>
-      <c r="C3" s="214"/>
-      <c r="D3" s="214"/>
-      <c r="E3" s="214"/>
-      <c r="F3" s="214"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="214"/>
-      <c r="I3" s="214"/>
-      <c r="J3" s="214"/>
+      <c r="B3" s="216"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="216"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
+      <c r="J3" s="216"/>
     </row>
     <row r="4" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="214"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="214"/>
-      <c r="E4" s="214"/>
-      <c r="F4" s="214"/>
-      <c r="G4" s="214"/>
-      <c r="H4" s="214"/>
-      <c r="I4" s="214"/>
-      <c r="J4" s="214"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="71"/>
@@ -32336,21 +34200,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B2" s="213" t="str">
+      <c r="B2" s="214" t="str">
         <f>"Historical Financial Statement - "&amp;'Data Sheet'!B1</f>
         <v>Historical Financial Statement - ASIAN PAINTS LTD</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
-      <c r="M2" s="213"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
+      <c r="L2" s="214"/>
+      <c r="M2" s="214"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
@@ -32453,7 +34317,7 @@
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
     </row>
-    <row r="6" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>1</v>
       </c>
@@ -32502,7 +34366,7 @@
         <v>34695.75</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
         <v>10</v>
       </c>
@@ -32548,8 +34412,8 @@
         <v>2.3303806271644634E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>59</v>
       </c>
@@ -32601,7 +34465,7 @@
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
     </row>
-    <row r="10" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>60</v>
       </c>
@@ -32650,8 +34514,8 @@
         <v>0.81710987656989698</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="27" t="s">
         <v>61</v>
       </c>
@@ -32700,7 +34564,7 @@
         <v>6345.5099999999984</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
         <v>62</v>
       </c>
@@ -32749,8 +34613,8 @@
         <v>0.18289012343010305</v>
       </c>
     </row>
-    <row r="14" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>63</v>
       </c>
@@ -32799,7 +34663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>64</v>
       </c>
@@ -32848,8 +34712,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>65</v>
       </c>
@@ -32898,7 +34762,7 @@
         <v>7802.5199999999995</v>
       </c>
     </row>
-    <row r="19" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
         <v>66</v>
       </c>
@@ -32947,8 +34811,8 @@
         <v>0.22488402758262899</v>
       </c>
     </row>
-    <row r="20" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>6</v>
       </c>
@@ -32997,7 +34861,7 @@
         <v>189.1</v>
       </c>
     </row>
-    <row r="22" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
         <v>67</v>
       </c>
@@ -33046,8 +34910,8 @@
         <v>5.4502352593617373E-3</v>
       </c>
     </row>
-    <row r="23" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>5</v>
       </c>
@@ -33096,7 +34960,7 @@
         <v>301.10000000000002</v>
       </c>
     </row>
-    <row r="25" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B25" s="15" t="s">
         <v>68</v>
       </c>
@@ -33145,8 +35009,8 @@
         <v>8.6782963331243738E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B27" s="27" t="s">
         <v>118</v>
       </c>
@@ -33195,7 +35059,7 @@
         <v>7312.32</v>
       </c>
     </row>
-    <row r="28" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B28" s="15" t="s">
         <v>69</v>
       </c>
@@ -33244,8 +35108,8 @@
         <v>0.21075549599014287</v>
       </c>
     </row>
-    <row r="29" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>8</v>
       </c>
@@ -33294,7 +35158,7 @@
         <v>1501.5400000000002</v>
       </c>
     </row>
-    <row r="31" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B31" s="15" t="s">
         <v>70</v>
       </c>
@@ -33343,8 +35207,8 @@
         <v>0.20534385803684743</v>
       </c>
     </row>
-    <row r="32" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="27" t="s">
         <v>71</v>
       </c>
@@ -33393,7 +35257,7 @@
         <v>5810.78</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="15" t="s">
         <v>72</v>
       </c>
@@ -33442,8 +35306,8 @@
         <v>0.16747814934105762</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>39</v>
       </c>
@@ -33492,8 +35356,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>73</v>
       </c>
@@ -33542,7 +35406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B39" s="15" t="s">
         <v>74</v>
       </c>
@@ -33588,8 +35452,8 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>75</v>
       </c>
@@ -33638,7 +35502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B42" s="15" t="s">
         <v>76</v>
       </c>
@@ -33687,8 +35551,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>77</v>
       </c>
@@ -33737,7 +35601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>77</v>
       </c>
@@ -33786,7 +35650,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" collapsed="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>58</v>
@@ -33806,7 +35669,7 @@
       <c r="L47" s="18"/>
       <c r="M47" s="18"/>
     </row>
-    <row r="48" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>11</v>
       </c>
@@ -33852,7 +35715,7 @@
       </c>
       <c r="M48" s="16"/>
     </row>
-    <row r="49" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>12</v>
       </c>
@@ -33898,7 +35761,7 @@
       </c>
       <c r="M49" s="16"/>
     </row>
-    <row r="50" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>36</v>
       </c>
@@ -33944,7 +35807,7 @@
       </c>
       <c r="M50" s="16"/>
     </row>
-    <row r="51" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>37</v>
       </c>
@@ -33990,7 +35853,7 @@
       </c>
       <c r="M51" s="16"/>
     </row>
-    <row r="52" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B52" s="29" t="s">
         <v>79</v>
       </c>
@@ -34036,10 +35899,10 @@
       </c>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>80</v>
       </c>
@@ -34085,7 +35948,7 @@
       </c>
       <c r="M54" s="16"/>
     </row>
-    <row r="55" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>15</v>
       </c>
@@ -34131,7 +35994,7 @@
       </c>
       <c r="M55" s="16"/>
     </row>
-    <row r="56" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>16</v>
       </c>
@@ -34177,7 +36040,7 @@
       </c>
       <c r="M56" s="16"/>
     </row>
-    <row r="57" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
         <v>38</v>
       </c>
@@ -34223,7 +36086,7 @@
       </c>
       <c r="M57" s="16"/>
     </row>
-    <row r="58" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B58" s="29" t="s">
         <v>81</v>
       </c>
@@ -34269,10 +36132,10 @@
       </c>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>43</v>
       </c>
@@ -34317,7 +36180,7 @@
         <v>4313.6499999999996</v>
       </c>
     </row>
-    <row r="61" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>30</v>
       </c>
@@ -34362,7 +36225,7 @@
         <v>6719.27</v>
       </c>
     </row>
-    <row r="62" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>52</v>
       </c>
@@ -34407,7 +36270,7 @@
         <v>781.98</v>
       </c>
     </row>
-    <row r="63" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B63" s="30" t="s">
         <v>82</v>
       </c>
@@ -34453,8 +36316,8 @@
       </c>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B65" s="31" t="s">
         <v>83</v>
       </c>
@@ -34499,8 +36362,8 @@
         <v>30355.25</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
-    <row r="67" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>84</v>
       </c>
@@ -34545,7 +36408,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:13" collapsed="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="22" t="s">
         <v>58</v>
@@ -36082,7 +37944,7 @@
   <pageMargins left="0.7" right="3.96" top="0.75" bottom="1.8" header="0.3" footer="0.26"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="M6 C15 D15:L15 M21 M18 M30 C57" formulaRange="1"/>
+    <ignoredError sqref="M6 C15:L15 M21 M18 M30 C57" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -36100,23 +37962,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="213" t="str">
+      <c r="B2" s="214" t="str">
         <f>"Ratio Analysis - "&amp;'Data Sheet'!B1</f>
         <v>Ratio Analysis - ASIAN PAINTS LTD</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
-      <c r="M2" s="213"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="213"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
+      <c r="L2" s="214"/>
+      <c r="M2" s="214"/>
+      <c r="N2" s="214"/>
+      <c r="O2" s="214"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
@@ -37882,7 +39744,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{808BD0CD-9C5A-4931-A0D8-E448E3D7A524}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{C730D17D-6083-47E0-BE4D-65602864D1AB}">
           <x14:colorSeries theme="7" tint="0.39997558519241921"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -37893,8 +39755,176 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>'Ratio Analysis'!D5:L5</xm:f>
-              <xm:sqref>M5</xm:sqref>
+              <xm:f>'Ratio Analysis'!C40:L40</xm:f>
+              <xm:sqref>M40</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C41:L41</xm:f>
+              <xm:sqref>M41</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C42:L42</xm:f>
+              <xm:sqref>M42</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{82FFBA1F-BA45-4BD7-B197-F861613E7C8C}">
+          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="1"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C35:L35</xm:f>
+              <xm:sqref>M35</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C36:L36</xm:f>
+              <xm:sqref>M36</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C37:L37</xm:f>
+              <xm:sqref>M37</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C38:L38</xm:f>
+              <xm:sqref>M38</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{486699F6-BFE3-4EEA-8384-DA9517688398}">
+          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="1"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C29:L29</xm:f>
+              <xm:sqref>M29</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C30:L30</xm:f>
+              <xm:sqref>M30</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C31:L31</xm:f>
+              <xm:sqref>M31</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C32:L32</xm:f>
+              <xm:sqref>M32</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C33:L33</xm:f>
+              <xm:sqref>M33</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{E20A6423-39C4-4DF3-807E-46E30CD98B3B}">
+          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="1"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C23:L23</xm:f>
+              <xm:sqref>M23</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C24:L24</xm:f>
+              <xm:sqref>M24</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C25:L25</xm:f>
+              <xm:sqref>M25</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C26:L26</xm:f>
+              <xm:sqref>M26</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C27:L27</xm:f>
+              <xm:sqref>M27</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{AA6F9BBC-A15B-4EC3-9919-CE22AD80622A}">
+          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="1"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C19:L19</xm:f>
+              <xm:sqref>M19</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C20:L20</xm:f>
+              <xm:sqref>M20</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C21:L21</xm:f>
+              <xm:sqref>M21</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{F0DAF7F1-2C0F-4223-9329-CEE62B5D2E95}">
+          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="1"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C13:L13</xm:f>
+              <xm:sqref>M13</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{69404CAD-1334-47E5-AD2F-9AD793FFE7C7}">
+          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="1"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C14:L14</xm:f>
+              <xm:sqref>M14</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C15:L15</xm:f>
+              <xm:sqref>M15</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C16:L16</xm:f>
+              <xm:sqref>M16</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Ratio Analysis'!C17:L17</xm:f>
+              <xm:sqref>M17</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -37934,7 +39964,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{69404CAD-1334-47E5-AD2F-9AD793FFE7C7}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{808BD0CD-9C5A-4931-A0D8-E448E3D7A524}">
           <x14:colorSeries theme="7" tint="0.39997558519241921"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -37945,176 +39975,8 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C14:L14</xm:f>
-              <xm:sqref>M14</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C15:L15</xm:f>
-              <xm:sqref>M15</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C16:L16</xm:f>
-              <xm:sqref>M16</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C17:L17</xm:f>
-              <xm:sqref>M17</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{F0DAF7F1-2C0F-4223-9329-CEE62B5D2E95}">
-          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="1"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C13:L13</xm:f>
-              <xm:sqref>M13</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{AA6F9BBC-A15B-4EC3-9919-CE22AD80622A}">
-          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="1"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C19:L19</xm:f>
-              <xm:sqref>M19</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C20:L20</xm:f>
-              <xm:sqref>M20</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C21:L21</xm:f>
-              <xm:sqref>M21</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{E20A6423-39C4-4DF3-807E-46E30CD98B3B}">
-          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="1"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C23:L23</xm:f>
-              <xm:sqref>M23</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C24:L24</xm:f>
-              <xm:sqref>M24</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C25:L25</xm:f>
-              <xm:sqref>M25</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C26:L26</xm:f>
-              <xm:sqref>M26</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C27:L27</xm:f>
-              <xm:sqref>M27</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{486699F6-BFE3-4EEA-8384-DA9517688398}">
-          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="1"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C29:L29</xm:f>
-              <xm:sqref>M29</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C30:L30</xm:f>
-              <xm:sqref>M30</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C31:L31</xm:f>
-              <xm:sqref>M31</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C32:L32</xm:f>
-              <xm:sqref>M32</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C33:L33</xm:f>
-              <xm:sqref>M33</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{82FFBA1F-BA45-4BD7-B197-F861613E7C8C}">
-          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="1"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C35:L35</xm:f>
-              <xm:sqref>M35</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C36:L36</xm:f>
-              <xm:sqref>M36</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C37:L37</xm:f>
-              <xm:sqref>M37</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C38:L38</xm:f>
-              <xm:sqref>M38</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" markers="1" xr2:uid="{C730D17D-6083-47E0-BE4D-65602864D1AB}">
-          <x14:colorSeries theme="7" tint="0.39997558519241921"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="1"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C40:L40</xm:f>
-              <xm:sqref>M40</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C41:L41</xm:f>
-              <xm:sqref>M41</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Ratio Analysis'!C42:L42</xm:f>
-              <xm:sqref>M42</xm:sqref>
+              <xm:f>'Ratio Analysis'!D5:L5</xm:f>
+              <xm:sqref>M5</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -38136,20 +39998,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="213" t="str">
+      <c r="B2" s="214" t="str">
         <f>"Common Size Income Statement"&amp;" "&amp;"- "&amp;'Data Sheet'!$B$1</f>
         <v>Common Size Income Statement - ASIAN PAINTS LTD</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="213"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
+      <c r="L2" s="214"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="64" t="s">
@@ -38939,20 +40801,20 @@
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="213" t="str">
+      <c r="B23" s="214" t="str">
         <f>"Common Size Balance Sheet"&amp;" "&amp;"- "&amp;'Data Sheet'!$B$1</f>
         <v>Common Size Balance Sheet - ASIAN PAINTS LTD</v>
       </c>
-      <c r="C23" s="213"/>
-      <c r="D23" s="213"/>
-      <c r="E23" s="213"/>
-      <c r="F23" s="213"/>
-      <c r="G23" s="213"/>
-      <c r="H23" s="213"/>
-      <c r="I23" s="213"/>
-      <c r="J23" s="213"/>
-      <c r="K23" s="213"/>
-      <c r="L23" s="213"/>
+      <c r="C23" s="214"/>
+      <c r="D23" s="214"/>
+      <c r="E23" s="214"/>
+      <c r="F23" s="214"/>
+      <c r="G23" s="214"/>
+      <c r="H23" s="214"/>
+      <c r="I23" s="214"/>
+      <c r="J23" s="214"/>
+      <c r="K23" s="214"/>
+      <c r="L23" s="214"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="64" t="s">
@@ -39621,7 +41483,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E81348-B1FB-41B8-8660-5A27E863EB68}">
-  <dimension ref="A1:AE51"/>
+  <dimension ref="A1:AE41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.88671875" customWidth="1"/>
@@ -39728,27 +41590,27 @@
       <c r="U5" s="183"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="B6" s="215" t="str">
+      <c r="B6" s="217" t="str">
         <f>'Data Sheet'!$B$1&amp;" - "&amp;'Data Sheet'!A17&amp;" Forecasting "</f>
         <v xml:space="preserve">ASIAN PAINTS LTD - Sales Forecasting </v>
       </c>
-      <c r="C6" s="215"/>
-      <c r="D6" s="215"/>
-      <c r="E6" s="215"/>
-      <c r="G6" s="215" t="str">
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="G6" s="217" t="str">
         <f>'Data Sheet'!$B$1&amp;" - "&amp;'Historical FS '!B18&amp;" Forecasting "</f>
         <v xml:space="preserve">ASIAN PAINTS LTD - EBITDA Forecasting </v>
       </c>
-      <c r="H6" s="215"/>
-      <c r="I6" s="215"/>
-      <c r="J6" s="215"/>
-      <c r="L6" s="215" t="str">
+      <c r="H6" s="217"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="217"/>
+      <c r="L6" s="217" t="str">
         <f>'Data Sheet'!$B$1&amp;" - "&amp;'Historical FS '!B38&amp;" Forecasting "</f>
         <v xml:space="preserve">ASIAN PAINTS LTD - Earning per Shares Forecasting </v>
       </c>
-      <c r="M6" s="215"/>
-      <c r="N6" s="215"/>
-      <c r="O6" s="215"/>
+      <c r="M6" s="217"/>
+      <c r="N6" s="217"/>
+      <c r="O6" s="217"/>
       <c r="T6" t="s">
         <v>171</v>
       </c>
@@ -39897,11 +41759,11 @@
     </row>
     <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="51">
-        <f t="shared" ref="B10:B27" si="0">B9+1</f>
+        <f t="shared" ref="B10:B22" si="0">B9+1</f>
         <v>3</v>
       </c>
       <c r="C10" s="52">
-        <f t="shared" ref="C10:C27" si="1">C9+365</f>
+        <f t="shared" ref="C10:C22" si="1">C9+365</f>
         <v>43190</v>
       </c>
       <c r="D10" s="53">
@@ -39912,11 +41774,11 @@
         <v>0.11702039371955486</v>
       </c>
       <c r="G10" s="51">
-        <f t="shared" ref="G10:G27" si="3">G9+1</f>
+        <f t="shared" ref="G10:G22" si="3">G9+1</f>
         <v>3</v>
       </c>
       <c r="H10" s="52">
-        <f t="shared" ref="H10:H27" si="4">H9+365</f>
+        <f t="shared" ref="H10:H22" si="4">H9+365</f>
         <v>43190</v>
       </c>
       <c r="I10" s="53">
@@ -39927,11 +41789,11 @@
         <v>7.0229410507188561E-2</v>
       </c>
       <c r="L10" s="51">
-        <f t="shared" ref="L10:L27" si="6">L9+1</f>
+        <f t="shared" ref="L10:L22" si="6">L9+1</f>
         <v>3</v>
       </c>
       <c r="M10" s="52">
-        <f t="shared" ref="M10:M27" si="7">M9+365</f>
+        <f t="shared" ref="M10:M22" si="7">M9+365</f>
         <v>43190</v>
       </c>
       <c r="N10" s="53">
@@ -40352,7 +42214,7 @@
         <v>38669.293333333335</v>
       </c>
       <c r="E18" s="58">
-        <f t="shared" ref="E18:E27" si="9">D18/D17-1</f>
+        <f t="shared" ref="E18:E22" si="9">D18/D17-1</f>
         <v>0.14049804526014653</v>
       </c>
       <c r="G18" s="55">
@@ -40364,7 +42226,7 @@
         <v>46110</v>
       </c>
       <c r="I18" s="57">
-        <f t="shared" ref="I18:I27" si="10">FORECAST(G18,$I$8:$I$17,$G$8:$G$17)</f>
+        <f t="shared" ref="I18:I22" si="10">FORECAST(G18,$I$8:$I$17,$G$8:$G$17)</f>
         <v>7328.2859999999991</v>
       </c>
       <c r="J18" s="58">
@@ -40380,7 +42242,7 @@
         <v>46110</v>
       </c>
       <c r="N18" s="57">
-        <f t="shared" ref="N18:N27" si="12">FORECAST(L18,$N$8:$N$17,$L$8:$L$17)</f>
+        <f t="shared" ref="N18:N22" si="12">FORECAST(L18,$N$8:$N$17,$L$8:$L$17)</f>
         <v>45.629295246038367</v>
       </c>
       <c r="O18" s="58">
@@ -40667,948 +42529,528 @@
         <v>5.7962351896612807E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B23" s="55">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C23" s="56">
-        <f t="shared" si="1"/>
-        <v>47935</v>
-      </c>
-      <c r="D23" s="57">
-        <f t="shared" ref="D23:D27" si="15">FORECAST(B23,$D$8:$D$17,$B$8:$B$17)</f>
-        <v>51976.612727272732</v>
-      </c>
-      <c r="E23" s="58">
-        <f t="shared" si="9"/>
-        <v>5.3968485159903379E-2</v>
-      </c>
-      <c r="G23" s="55">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="H23" s="56">
-        <f t="shared" si="4"/>
-        <v>47935</v>
-      </c>
-      <c r="I23" s="57">
-        <f t="shared" si="10"/>
-        <v>9775.3296363636364</v>
-      </c>
-      <c r="J23" s="58">
-        <f t="shared" ref="J23:J27" si="16">I23/I22-1</f>
-        <v>5.2704382480104561E-2</v>
-      </c>
-      <c r="L23" s="55">
-        <f t="shared" si="6"/>
-        <v>16</v>
-      </c>
-      <c r="M23" s="56">
-        <f t="shared" si="7"/>
-        <v>47935</v>
-      </c>
-      <c r="N23" s="57">
-        <f t="shared" si="12"/>
-        <v>61.636678292516493</v>
-      </c>
-      <c r="O23" s="58">
-        <f t="shared" ref="O23:O27" si="17">N23/N22-1</f>
-        <v>5.4786781205119039E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B24" s="55">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C24" s="56">
-        <f t="shared" si="1"/>
-        <v>48300</v>
-      </c>
-      <c r="D24" s="57">
-        <f t="shared" si="15"/>
-        <v>54638.076606060611</v>
-      </c>
-      <c r="E24" s="58">
-        <f t="shared" si="9"/>
-        <v>5.1205027398627978E-2</v>
-      </c>
-      <c r="G24" s="55">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-      <c r="H24" s="56">
-        <f t="shared" si="4"/>
-        <v>48300</v>
-      </c>
-      <c r="I24" s="57">
-        <f t="shared" si="10"/>
-        <v>10264.738363636363</v>
-      </c>
-      <c r="J24" s="58">
-        <f t="shared" si="16"/>
-        <v>5.0065700644217115E-2</v>
-      </c>
-      <c r="L24" s="55">
-        <f t="shared" si="6"/>
-        <v>17</v>
-      </c>
-      <c r="M24" s="56">
-        <f t="shared" si="7"/>
-        <v>48300</v>
-      </c>
-      <c r="N24" s="57">
-        <f t="shared" si="12"/>
-        <v>64.838154901812118</v>
-      </c>
-      <c r="O24" s="58">
-        <f t="shared" si="17"/>
-        <v>5.1941095756361078E-2</v>
-      </c>
-    </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B25" s="55">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C25" s="56">
-        <f t="shared" si="1"/>
-        <v>48665</v>
-      </c>
-      <c r="D25" s="57">
-        <f t="shared" si="15"/>
-        <v>57299.54048484849</v>
-      </c>
-      <c r="E25" s="58">
-        <f t="shared" si="9"/>
-        <v>4.8710790059045772E-2</v>
-      </c>
-      <c r="G25" s="55">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="H25" s="56">
-        <f t="shared" si="4"/>
-        <v>48665</v>
-      </c>
-      <c r="I25" s="57">
-        <f t="shared" si="10"/>
-        <v>10754.147090909089</v>
-      </c>
-      <c r="J25" s="58">
-        <f t="shared" si="16"/>
-        <v>4.7678636311520251E-2</v>
-      </c>
-      <c r="L25" s="55">
-        <f t="shared" si="6"/>
-        <v>18</v>
-      </c>
-      <c r="M25" s="56">
-        <f t="shared" si="7"/>
-        <v>48665</v>
-      </c>
-      <c r="N25" s="57">
-        <f t="shared" si="12"/>
-        <v>68.039631511107743</v>
-      </c>
-      <c r="O25" s="58">
-        <f t="shared" si="17"/>
-        <v>4.9376429883666306E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B26" s="55">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C26" s="56">
-        <f t="shared" si="1"/>
-        <v>49030</v>
-      </c>
-      <c r="D26" s="57">
-        <f t="shared" si="15"/>
-        <v>59961.00436363637</v>
-      </c>
-      <c r="E26" s="58">
-        <f t="shared" si="9"/>
-        <v>4.6448258681788923E-2</v>
-      </c>
-      <c r="G26" s="55">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-      <c r="H26" s="56">
-        <f t="shared" si="4"/>
-        <v>49030</v>
-      </c>
-      <c r="I26" s="57">
-        <f t="shared" si="10"/>
-        <v>11243.555818181816</v>
-      </c>
-      <c r="J26" s="58">
-        <f t="shared" si="16"/>
-        <v>4.5508837022179449E-2</v>
-      </c>
-      <c r="L26" s="55">
-        <f t="shared" si="6"/>
-        <v>19</v>
-      </c>
-      <c r="M26" s="56">
-        <f t="shared" si="7"/>
-        <v>49030</v>
-      </c>
-      <c r="N26" s="57">
-        <f t="shared" si="12"/>
-        <v>71.241108120403368</v>
-      </c>
-      <c r="O26" s="58">
-        <f t="shared" si="17"/>
-        <v>4.7053115047705374E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B27" s="55">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C27" s="56">
-        <f t="shared" si="1"/>
-        <v>49395</v>
-      </c>
-      <c r="D27" s="57">
-        <f t="shared" si="15"/>
-        <v>62622.468242424249</v>
-      </c>
-      <c r="E27" s="58">
-        <f t="shared" si="9"/>
-        <v>4.4386579361601397E-2</v>
-      </c>
-      <c r="G27" s="55">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="H27" s="56">
-        <f t="shared" si="4"/>
-        <v>49395</v>
-      </c>
-      <c r="I27" s="57">
-        <f t="shared" si="10"/>
-        <v>11732.964545454546</v>
-      </c>
-      <c r="J27" s="58">
-        <f t="shared" si="16"/>
-        <v>4.3527931482433058E-2</v>
-      </c>
-      <c r="L27" s="55">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="M27" s="56">
-        <f t="shared" si="7"/>
-        <v>49395</v>
-      </c>
-      <c r="N27" s="57">
-        <f t="shared" si="12"/>
-        <v>74.442584729698979</v>
-      </c>
-      <c r="O27" s="58">
-        <f t="shared" si="17"/>
-        <v>4.4938613305745445E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B30" s="215" t="str">
+      <c r="B25" s="217" t="str">
         <f>'Data Sheet'!$B$1&amp;" - "&amp;'Data Sheet'!A34&amp;" Forecasting "</f>
         <v xml:space="preserve">ASIAN PAINTS LTD - EBIT Forecasting </v>
       </c>
-      <c r="C30" s="215"/>
-      <c r="D30" s="215"/>
-      <c r="E30" s="215"/>
-      <c r="G30" s="215" t="str">
+      <c r="C25" s="217"/>
+      <c r="D25" s="217"/>
+      <c r="E25" s="217"/>
+      <c r="G25" s="217" t="str">
         <f>'Data Sheet'!$B$1&amp;" - "&amp;'Historical FS '!B33&amp;" Forecasting "</f>
         <v xml:space="preserve">ASIAN PAINTS LTD - Net Profit Forecasting </v>
       </c>
-      <c r="H30" s="215"/>
-      <c r="I30" s="215"/>
-      <c r="J30" s="215"/>
+      <c r="H25" s="217"/>
+      <c r="I25" s="217"/>
+      <c r="J25" s="217"/>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B26" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>289</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="I26" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="50" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B27" s="51">
+        <v>1</v>
+      </c>
+      <c r="C27" s="52">
+        <f>'Data Sheet'!$B$16</f>
+        <v>42460</v>
+      </c>
+      <c r="D27" s="53" cm="1">
+        <f t="array" ref="D27:D36">TRANSPOSE('Data Sheet'!B34:K34)</f>
+        <v>2638.65</v>
+      </c>
+      <c r="G27" s="51">
+        <v>1</v>
+      </c>
+      <c r="H27" s="52">
+        <f>'Data Sheet'!$B$16</f>
+        <v>42460</v>
+      </c>
+      <c r="I27" s="53">
+        <f t="array" ref="I27:I36">TRANSPOSE('Historical FS '!C33:L33)</f>
+        <v>1555.9700000000014</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B28" s="51">
+        <f>B27+1</f>
+        <v>2</v>
+      </c>
+      <c r="C28" s="52">
+        <f>C27+365</f>
+        <v>42825</v>
+      </c>
+      <c r="D28" s="53">
+        <v>2920.05</v>
+      </c>
+      <c r="E28" s="54">
+        <f>D28/D27-1</f>
+        <v>0.10664544369279749</v>
+      </c>
+      <c r="G28" s="51">
+        <f>G27+1</f>
+        <v>2</v>
+      </c>
+      <c r="H28" s="52">
+        <f>H27+365</f>
+        <v>42825</v>
+      </c>
+      <c r="I28" s="53">
+        <v>1678.3500000000004</v>
+      </c>
+      <c r="J28" s="54">
+        <f>I28/I27-1</f>
+        <v>7.8651902028958665E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B29" s="51">
+        <f t="shared" ref="B29:B41" si="15">B28+1</f>
+        <v>3</v>
+      </c>
+      <c r="C29" s="52">
+        <f t="shared" ref="C29:C41" si="16">C28+365</f>
+        <v>43190</v>
+      </c>
+      <c r="D29" s="53">
+        <v>3121.3599999999997</v>
+      </c>
+      <c r="E29" s="54">
+        <f t="shared" ref="E29:E41" si="17">D29/D28-1</f>
+        <v>6.8940600332185964E-2</v>
+      </c>
+      <c r="G29" s="51">
+        <f t="shared" ref="G29:G41" si="18">G28+1</f>
+        <v>3</v>
+      </c>
+      <c r="H29" s="52">
+        <f t="shared" ref="H29:H41" si="19">H28+365</f>
+        <v>43190</v>
+      </c>
+      <c r="I29" s="53">
+        <v>1761.110000000001</v>
+      </c>
+      <c r="J29" s="54">
+        <f t="shared" ref="J29:J35" si="20">I29/I28-1</f>
+        <v>4.9310334554771407E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B30" s="51">
+        <f t="shared" si="15"/>
+        <v>4</v>
+      </c>
+      <c r="C30" s="52">
+        <f t="shared" si="16"/>
+        <v>43555</v>
+      </c>
+      <c r="D30" s="53">
+        <v>3364.45</v>
+      </c>
+      <c r="E30" s="54">
+        <f t="shared" si="17"/>
+        <v>7.7879514057974886E-2</v>
+      </c>
+      <c r="G30" s="51">
+        <f t="shared" si="18"/>
+        <v>4</v>
+      </c>
+      <c r="H30" s="52">
+        <f t="shared" si="19"/>
+        <v>43555</v>
+      </c>
+      <c r="I30" s="53">
+        <v>1934.2700000000013</v>
+      </c>
+      <c r="J30" s="54">
+        <f t="shared" si="20"/>
+        <v>9.8324352255112046E-2</v>
+      </c>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B31" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="50" t="s">
-        <v>289</v>
-      </c>
-      <c r="E31" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="G31" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="J31" s="50" t="s">
-        <v>154</v>
+      <c r="B31" s="51">
+        <f t="shared" si="15"/>
+        <v>5</v>
+      </c>
+      <c r="C31" s="52">
+        <f t="shared" si="16"/>
+        <v>43920</v>
+      </c>
+      <c r="D31" s="53">
+        <v>3667.9699999999993</v>
+      </c>
+      <c r="E31" s="54">
+        <f t="shared" si="17"/>
+        <v>9.021385367593493E-2</v>
+      </c>
+      <c r="G31" s="51">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="H31" s="52">
+        <f t="shared" si="19"/>
+        <v>43920</v>
+      </c>
+      <c r="I31" s="53">
+        <v>2424.0899999999979</v>
+      </c>
+      <c r="J31" s="54">
+        <f t="shared" si="20"/>
+        <v>0.25323248564057566</v>
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B32" s="51">
-        <v>1</v>
+        <f t="shared" si="15"/>
+        <v>6</v>
       </c>
       <c r="C32" s="52">
-        <f>'Data Sheet'!$B$16</f>
-        <v>42460</v>
-      </c>
-      <c r="D32" s="53" cm="1">
-        <f t="array" ref="D32:D41">TRANSPOSE('Data Sheet'!B34:K34)</f>
-        <v>2638.65</v>
+        <f t="shared" si="16"/>
+        <v>44285</v>
+      </c>
+      <c r="D32" s="53">
+        <v>4328.5199999999986</v>
+      </c>
+      <c r="E32" s="54">
+        <f t="shared" si="17"/>
+        <v>0.18008598761712857</v>
       </c>
       <c r="G32" s="51">
-        <v>1</v>
+        <f t="shared" si="18"/>
+        <v>6</v>
       </c>
       <c r="H32" s="52">
-        <f>'Data Sheet'!$B$16</f>
-        <v>42460</v>
+        <f t="shared" si="19"/>
+        <v>44285</v>
       </c>
       <c r="I32" s="53">
-        <f t="array" ref="I32:I41">TRANSPOSE('Historical FS '!C33:L33)</f>
-        <v>1555.9700000000014</v>
+        <v>2875.1000000000031</v>
+      </c>
+      <c r="J32" s="54">
+        <f t="shared" si="20"/>
+        <v>0.1860533231026924</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="51">
-        <f>B32+1</f>
-        <v>2</v>
+        <f t="shared" si="15"/>
+        <v>7</v>
       </c>
       <c r="C33" s="52">
-        <f>C32+365</f>
-        <v>42825</v>
+        <f t="shared" si="16"/>
+        <v>44650</v>
       </c>
       <c r="D33" s="53">
-        <v>2920.05</v>
+        <v>4228.8900000000003</v>
       </c>
       <c r="E33" s="54">
-        <f>D33/D32-1</f>
-        <v>0.10664544369279749</v>
+        <f t="shared" si="17"/>
+        <v>-2.3017105153724238E-2</v>
       </c>
       <c r="G33" s="51">
-        <f>G32+1</f>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>7</v>
       </c>
       <c r="H33" s="52">
-        <f>H32+365</f>
-        <v>42825</v>
+        <f t="shared" si="19"/>
+        <v>44650</v>
       </c>
       <c r="I33" s="53">
-        <v>1678.3500000000004</v>
+        <v>2788.9299999999985</v>
       </c>
       <c r="J33" s="54">
-        <f>I33/I32-1</f>
-        <v>7.8651902028958665E-2</v>
+        <f t="shared" si="20"/>
+        <v>-2.9971131438908061E-2</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="51">
-        <f t="shared" ref="B34:B51" si="18">B33+1</f>
-        <v>3</v>
+        <f t="shared" si="15"/>
+        <v>8</v>
       </c>
       <c r="C34" s="52">
-        <f t="shared" ref="C34:C51" si="19">C33+365</f>
-        <v>43190</v>
+        <f t="shared" si="16"/>
+        <v>45015</v>
       </c>
       <c r="D34" s="53">
-        <v>3121.3599999999997</v>
+        <v>5744.4</v>
       </c>
       <c r="E34" s="54">
-        <f t="shared" ref="E34:E51" si="20">D34/D33-1</f>
-        <v>6.8940600332185964E-2</v>
+        <f t="shared" si="17"/>
+        <v>0.35837063626625398</v>
       </c>
       <c r="G34" s="51">
-        <f t="shared" ref="G34:G51" si="21">G33+1</f>
-        <v>3</v>
+        <f t="shared" si="18"/>
+        <v>8</v>
       </c>
       <c r="H34" s="52">
-        <f t="shared" ref="H34:H51" si="22">H33+365</f>
-        <v>43190</v>
+        <f t="shared" si="19"/>
+        <v>45015</v>
       </c>
       <c r="I34" s="53">
-        <v>1761.110000000001</v>
+        <v>3763.8699999999953</v>
       </c>
       <c r="J34" s="54">
-        <f t="shared" ref="J34:J40" si="23">I34/I33-1</f>
-        <v>4.9310334554771407E-2</v>
+        <f t="shared" si="20"/>
+        <v>0.34957492658474654</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="51">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C35" s="52">
+        <f t="shared" si="16"/>
+        <v>45380</v>
+      </c>
+      <c r="D35" s="53">
+        <v>7455.48</v>
+      </c>
+      <c r="E35" s="54">
+        <f t="shared" si="17"/>
+        <v>0.29786922916231462</v>
+      </c>
+      <c r="G35" s="51">
         <f t="shared" si="18"/>
-        <v>4</v>
-      </c>
-      <c r="C35" s="52">
+        <v>9</v>
+      </c>
+      <c r="H35" s="52">
         <f t="shared" si="19"/>
-        <v>43555</v>
-      </c>
-      <c r="D35" s="53">
-        <v>3364.45</v>
-      </c>
-      <c r="E35" s="54">
+        <v>45380</v>
+      </c>
+      <c r="I35" s="53">
+        <v>4736.7300000000014</v>
+      </c>
+      <c r="J35" s="54">
         <f t="shared" si="20"/>
-        <v>7.7879514057974886E-2</v>
-      </c>
-      <c r="G35" s="51">
-        <f t="shared" si="21"/>
-        <v>4</v>
-      </c>
-      <c r="H35" s="52">
-        <f t="shared" si="22"/>
-        <v>43555</v>
-      </c>
-      <c r="I35" s="53">
-        <v>1934.2700000000013</v>
-      </c>
-      <c r="J35" s="54">
-        <f t="shared" si="23"/>
-        <v>9.8324352255112046E-2</v>
+        <v>0.25847332665581102</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="51">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="15"/>
+        <v>10</v>
       </c>
       <c r="C36" s="52">
-        <f t="shared" si="19"/>
-        <v>43920</v>
+        <f t="shared" si="16"/>
+        <v>45745</v>
       </c>
       <c r="D36" s="53">
-        <v>3667.9699999999993</v>
+        <v>5287.6100000000006</v>
       </c>
       <c r="E36" s="54">
-        <f t="shared" si="20"/>
-        <v>9.021385367593493E-2</v>
+        <f t="shared" si="17"/>
+        <v>-0.29077537596506187</v>
       </c>
       <c r="G36" s="51">
-        <f t="shared" si="21"/>
-        <v>5</v>
-      </c>
-      <c r="H36" s="52">
-        <f t="shared" si="22"/>
-        <v>43920</v>
-      </c>
-      <c r="I36" s="53">
-        <v>2424.0899999999979</v>
-      </c>
-      <c r="J36" s="54">
-        <f t="shared" si="23"/>
-        <v>0.25323248564057566</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" s="51">
-        <f t="shared" si="18"/>
-        <v>6</v>
-      </c>
-      <c r="C37" s="52">
-        <f t="shared" si="19"/>
-        <v>44285</v>
-      </c>
-      <c r="D37" s="53">
-        <v>4328.5199999999986</v>
-      </c>
-      <c r="E37" s="54">
-        <f t="shared" si="20"/>
-        <v>0.18008598761712857</v>
-      </c>
-      <c r="G37" s="51">
-        <f t="shared" si="21"/>
-        <v>6</v>
-      </c>
-      <c r="H37" s="52">
-        <f t="shared" si="22"/>
-        <v>44285</v>
-      </c>
-      <c r="I37" s="53">
-        <v>2875.1000000000031</v>
-      </c>
-      <c r="J37" s="54">
-        <f t="shared" si="23"/>
-        <v>0.1860533231026924</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B38" s="51">
-        <f t="shared" si="18"/>
-        <v>7</v>
-      </c>
-      <c r="C38" s="52">
-        <f t="shared" si="19"/>
-        <v>44650</v>
-      </c>
-      <c r="D38" s="53">
-        <v>4228.8900000000003</v>
-      </c>
-      <c r="E38" s="54">
-        <f t="shared" si="20"/>
-        <v>-2.3017105153724238E-2</v>
-      </c>
-      <c r="G38" s="51">
-        <f t="shared" si="21"/>
-        <v>7</v>
-      </c>
-      <c r="H38" s="52">
-        <f t="shared" si="22"/>
-        <v>44650</v>
-      </c>
-      <c r="I38" s="53">
-        <v>2788.9299999999985</v>
-      </c>
-      <c r="J38" s="54">
-        <f t="shared" si="23"/>
-        <v>-2.9971131438908061E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B39" s="51">
-        <f t="shared" si="18"/>
-        <v>8</v>
-      </c>
-      <c r="C39" s="52">
-        <f t="shared" si="19"/>
-        <v>45015</v>
-      </c>
-      <c r="D39" s="53">
-        <v>5744.4</v>
-      </c>
-      <c r="E39" s="54">
-        <f t="shared" si="20"/>
-        <v>0.35837063626625398</v>
-      </c>
-      <c r="G39" s="51">
-        <f t="shared" si="21"/>
-        <v>8</v>
-      </c>
-      <c r="H39" s="52">
-        <f t="shared" si="22"/>
-        <v>45015</v>
-      </c>
-      <c r="I39" s="53">
-        <v>3763.8699999999953</v>
-      </c>
-      <c r="J39" s="54">
-        <f t="shared" si="23"/>
-        <v>0.34957492658474654</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="51">
-        <f t="shared" si="18"/>
-        <v>9</v>
-      </c>
-      <c r="C40" s="52">
-        <f t="shared" si="19"/>
-        <v>45380</v>
-      </c>
-      <c r="D40" s="53">
-        <v>7455.48</v>
-      </c>
-      <c r="E40" s="54">
-        <f t="shared" si="20"/>
-        <v>0.29786922916231462</v>
-      </c>
-      <c r="G40" s="51">
-        <f t="shared" si="21"/>
-        <v>9</v>
-      </c>
-      <c r="H40" s="52">
-        <f t="shared" si="22"/>
-        <v>45380</v>
-      </c>
-      <c r="I40" s="53">
-        <v>4736.7300000000014</v>
-      </c>
-      <c r="J40" s="54">
-        <f t="shared" si="23"/>
-        <v>0.25847332665581102</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B41" s="51">
         <f t="shared" si="18"/>
         <v>10</v>
       </c>
-      <c r="C41" s="52">
+      <c r="H36" s="52">
         <f t="shared" si="19"/>
         <v>45745</v>
       </c>
-      <c r="D41" s="53">
-        <v>5287.6100000000006</v>
-      </c>
-      <c r="E41" s="54">
-        <f t="shared" si="20"/>
-        <v>-0.29077537596506187</v>
-      </c>
-      <c r="G41" s="51">
-        <f t="shared" si="21"/>
-        <v>10</v>
-      </c>
-      <c r="H41" s="52">
-        <f t="shared" si="22"/>
-        <v>45745</v>
-      </c>
-      <c r="I41" s="53">
+      <c r="I36" s="53">
         <v>3359.4900000000025</v>
       </c>
-      <c r="J41" s="54">
-        <f>I41/I40-1</f>
+      <c r="J36" s="54">
+        <f>I36/I35-1</f>
         <v>-0.29075754792863395</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B42" s="55">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="55">
+        <f t="shared" si="15"/>
+        <v>11</v>
+      </c>
+      <c r="C37" s="56">
+        <f t="shared" si="16"/>
+        <v>46110</v>
+      </c>
+      <c r="D37" s="57">
+        <f t="shared" ref="D37:D41" si="21">FORECAST(B37,$D$27:$D$36,$B$27:$B$36)</f>
+        <v>6674.3286666666663</v>
+      </c>
+      <c r="E37" s="58">
+        <f t="shared" si="17"/>
+        <v>0.26225812165924967</v>
+      </c>
+      <c r="G37" s="55">
         <f t="shared" si="18"/>
         <v>11</v>
       </c>
-      <c r="C42" s="56">
+      <c r="H37" s="56">
         <f t="shared" si="19"/>
         <v>46110</v>
       </c>
-      <c r="D42" s="57">
-        <f t="shared" ref="D42:D51" si="24">FORECAST(B42,$D$32:$D$41,$B$32:$B$41)</f>
-        <v>6674.3286666666663</v>
-      </c>
-      <c r="E42" s="58">
-        <f t="shared" si="20"/>
-        <v>0.26225812165924967</v>
-      </c>
-      <c r="G42" s="55">
+      <c r="I37" s="57">
+        <f t="shared" ref="I37:I41" si="22">FORECAST(G37,$I$27:$I$36,$G$27:$G$36)</f>
+        <v>4376.7619999999997</v>
+      </c>
+      <c r="J37" s="58">
+        <f>I37/I36-1</f>
+        <v>0.30280548535640728</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B38" s="55">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="C38" s="56">
+        <f t="shared" si="16"/>
+        <v>46475</v>
+      </c>
+      <c r="D38" s="57">
         <f t="shared" si="21"/>
-        <v>11</v>
-      </c>
-      <c r="H42" s="56">
-        <f t="shared" si="22"/>
-        <v>46110</v>
-      </c>
-      <c r="I42" s="57">
-        <f t="shared" ref="I42:I51" si="25">FORECAST(G42,$I$32:$I$41,$G$32:$G$41)</f>
-        <v>4376.7619999999997</v>
-      </c>
-      <c r="J42" s="58">
-        <f>I42/I41-1</f>
-        <v>0.30280548535640728</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B43" s="55">
+        <v>7110.4360606060618</v>
+      </c>
+      <c r="E38" s="58">
+        <f t="shared" si="17"/>
+        <v>6.5341012665053322E-2</v>
+      </c>
+      <c r="G38" s="55">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="C43" s="56">
+      <c r="H38" s="56">
         <f t="shared" si="19"/>
         <v>46475</v>
       </c>
-      <c r="D43" s="57">
-        <f t="shared" si="24"/>
-        <v>7110.4360606060618</v>
-      </c>
-      <c r="E43" s="58">
-        <f t="shared" si="20"/>
-        <v>6.5341012665053322E-2</v>
-      </c>
-      <c r="G43" s="55">
+      <c r="I38" s="57">
+        <f t="shared" si="22"/>
+        <v>4683.8476363636355</v>
+      </c>
+      <c r="J38" s="58">
+        <f>I38/I37-1</f>
+        <v>7.0162745052994913E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B39" s="55">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="C39" s="56">
+        <f t="shared" si="16"/>
+        <v>46840</v>
+      </c>
+      <c r="D39" s="57">
         <f t="shared" si="21"/>
-        <v>12</v>
-      </c>
-      <c r="H43" s="56">
-        <f t="shared" si="22"/>
-        <v>46475</v>
-      </c>
-      <c r="I43" s="57">
-        <f t="shared" si="25"/>
-        <v>4683.8476363636355</v>
-      </c>
-      <c r="J43" s="58">
-        <f>I43/I42-1</f>
-        <v>7.0162745052994913E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B44" s="55">
+        <v>7546.5434545454555</v>
+      </c>
+      <c r="E39" s="58">
+        <f t="shared" si="17"/>
+        <v>6.1333424591996311E-2</v>
+      </c>
+      <c r="G39" s="55">
         <f t="shared" si="18"/>
         <v>13</v>
       </c>
-      <c r="C44" s="56">
+      <c r="H39" s="56">
         <f t="shared" si="19"/>
         <v>46840</v>
       </c>
-      <c r="D44" s="57">
-        <f t="shared" si="24"/>
-        <v>7546.5434545454555</v>
-      </c>
-      <c r="E44" s="58">
-        <f t="shared" si="20"/>
-        <v>6.1333424591996311E-2</v>
-      </c>
-      <c r="G44" s="55">
+      <c r="I39" s="57">
+        <f t="shared" si="22"/>
+        <v>4990.9332727272722</v>
+      </c>
+      <c r="J39" s="58">
+        <f>I39/I38-1</f>
+        <v>6.5562686962645556E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B40" s="55">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="C40" s="56">
+        <f t="shared" si="16"/>
+        <v>47205</v>
+      </c>
+      <c r="D40" s="57">
         <f t="shared" si="21"/>
-        <v>13</v>
-      </c>
-      <c r="H44" s="56">
-        <f t="shared" si="22"/>
-        <v>46840</v>
-      </c>
-      <c r="I44" s="57">
-        <f t="shared" si="25"/>
-        <v>4990.9332727272722</v>
-      </c>
-      <c r="J44" s="58">
-        <f>I44/I43-1</f>
-        <v>6.5562686962645556E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B45" s="55">
+        <v>7982.6508484848491</v>
+      </c>
+      <c r="E40" s="58">
+        <f t="shared" si="17"/>
+        <v>5.7789025739554578E-2</v>
+      </c>
+      <c r="G40" s="55">
         <f t="shared" si="18"/>
         <v>14</v>
       </c>
-      <c r="C45" s="56">
+      <c r="H40" s="56">
         <f t="shared" si="19"/>
         <v>47205</v>
       </c>
-      <c r="D45" s="57">
-        <f t="shared" si="24"/>
-        <v>7982.6508484848491</v>
-      </c>
-      <c r="E45" s="58">
-        <f t="shared" si="20"/>
-        <v>5.7789025739554578E-2</v>
-      </c>
-      <c r="G45" s="55">
+      <c r="I40" s="57">
+        <f t="shared" si="22"/>
+        <v>5298.018909090908</v>
+      </c>
+      <c r="J40" s="58">
+        <f t="shared" ref="J40:J41" si="23">I40/I39-1</f>
+        <v>6.1528700061307395E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B41" s="55">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="C41" s="56">
+        <f t="shared" si="16"/>
+        <v>47570</v>
+      </c>
+      <c r="D41" s="57">
         <f t="shared" si="21"/>
-        <v>14</v>
-      </c>
-      <c r="H45" s="56">
-        <f t="shared" si="22"/>
-        <v>47205</v>
-      </c>
-      <c r="I45" s="57">
-        <f t="shared" si="25"/>
-        <v>5298.018909090908</v>
-      </c>
-      <c r="J45" s="58">
-        <f t="shared" ref="J45:J46" si="26">I45/I44-1</f>
-        <v>6.1528700061307395E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" s="55">
+        <v>8418.7582424242428</v>
+      </c>
+      <c r="E41" s="58">
+        <f t="shared" si="17"/>
+        <v>5.4631901384258663E-2</v>
+      </c>
+      <c r="G41" s="55">
         <f t="shared" si="18"/>
         <v>15</v>
       </c>
-      <c r="C46" s="56">
+      <c r="H41" s="56">
         <f t="shared" si="19"/>
         <v>47570</v>
       </c>
-      <c r="D46" s="57">
-        <f t="shared" si="24"/>
-        <v>8418.7582424242428</v>
-      </c>
-      <c r="E46" s="58">
-        <f t="shared" si="20"/>
-        <v>5.4631901384258663E-2</v>
-      </c>
-      <c r="G46" s="55">
-        <f t="shared" si="21"/>
-        <v>15</v>
-      </c>
-      <c r="H46" s="56">
+      <c r="I41" s="57">
         <f t="shared" si="22"/>
-        <v>47570</v>
-      </c>
-      <c r="I46" s="57">
-        <f t="shared" si="25"/>
         <v>5605.1045454545447</v>
       </c>
-      <c r="J46" s="58">
-        <f t="shared" si="26"/>
+      <c r="J41" s="58">
+        <f t="shared" si="23"/>
         <v>5.7962351896613029E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" s="55">
-        <f t="shared" si="18"/>
-        <v>16</v>
-      </c>
-      <c r="C47" s="56">
-        <f t="shared" si="19"/>
-        <v>47935</v>
-      </c>
-      <c r="D47" s="57">
-        <f t="shared" si="24"/>
-        <v>8854.8656363636364</v>
-      </c>
-      <c r="E47" s="58">
-        <f t="shared" si="20"/>
-        <v>5.180186690024402E-2</v>
-      </c>
-      <c r="G47" s="55">
-        <f t="shared" si="21"/>
-        <v>16</v>
-      </c>
-      <c r="H47" s="56">
-        <f t="shared" si="22"/>
-        <v>47935</v>
-      </c>
-      <c r="I47" s="57">
-        <f t="shared" si="25"/>
-        <v>5912.1901818181805</v>
-      </c>
-      <c r="J47" s="58">
-        <f t="shared" ref="J47:J51" si="27">I47/I46-1</f>
-        <v>5.4786781205119039E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B48" s="55">
-        <f t="shared" si="18"/>
-        <v>17</v>
-      </c>
-      <c r="C48" s="56">
-        <f t="shared" si="19"/>
-        <v>48300</v>
-      </c>
-      <c r="D48" s="57">
-        <f t="shared" si="24"/>
-        <v>9290.9730303030301</v>
-      </c>
-      <c r="E48" s="58">
-        <f t="shared" si="20"/>
-        <v>4.9250594175981988E-2</v>
-      </c>
-      <c r="G48" s="55">
-        <f t="shared" si="21"/>
-        <v>17</v>
-      </c>
-      <c r="H48" s="56">
-        <f t="shared" si="22"/>
-        <v>48300</v>
-      </c>
-      <c r="I48" s="57">
-        <f t="shared" si="25"/>
-        <v>6219.2758181818162</v>
-      </c>
-      <c r="J48" s="58">
-        <f t="shared" si="27"/>
-        <v>5.1941095756361078E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B49" s="55">
-        <f t="shared" si="18"/>
-        <v>18</v>
-      </c>
-      <c r="C49" s="56">
-        <f t="shared" si="19"/>
-        <v>48665</v>
-      </c>
-      <c r="D49" s="57">
-        <f t="shared" si="24"/>
-        <v>9727.0804242424256</v>
-      </c>
-      <c r="E49" s="58">
-        <f t="shared" si="20"/>
-        <v>4.6938828959787848E-2</v>
-      </c>
-      <c r="G49" s="55">
-        <f t="shared" si="21"/>
-        <v>18</v>
-      </c>
-      <c r="H49" s="56">
-        <f t="shared" si="22"/>
-        <v>48665</v>
-      </c>
-      <c r="I49" s="57">
-        <f t="shared" si="25"/>
-        <v>6526.3614545454529</v>
-      </c>
-      <c r="J49" s="58">
-        <f t="shared" si="27"/>
-        <v>4.9376429883666528E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B50" s="55">
-        <f t="shared" si="18"/>
-        <v>19</v>
-      </c>
-      <c r="C50" s="56">
-        <f t="shared" si="19"/>
-        <v>49030</v>
-      </c>
-      <c r="D50" s="57">
-        <f t="shared" si="24"/>
-        <v>10163.187818181819</v>
-      </c>
-      <c r="E50" s="58">
-        <f t="shared" si="20"/>
-        <v>4.4834356756473515E-2</v>
-      </c>
-      <c r="G50" s="55">
-        <f t="shared" si="21"/>
-        <v>19</v>
-      </c>
-      <c r="H50" s="56">
-        <f t="shared" si="22"/>
-        <v>49030</v>
-      </c>
-      <c r="I50" s="57">
-        <f t="shared" si="25"/>
-        <v>6833.4470909090896</v>
-      </c>
-      <c r="J50" s="58">
-        <f t="shared" si="27"/>
-        <v>4.7053115047705374E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B51" s="55">
-        <f t="shared" si="18"/>
-        <v>20</v>
-      </c>
-      <c r="C51" s="56">
-        <f t="shared" si="19"/>
-        <v>49395</v>
-      </c>
-      <c r="D51" s="57">
-        <f t="shared" si="24"/>
-        <v>10599.295212121213</v>
-      </c>
-      <c r="E51" s="58">
-        <f t="shared" si="20"/>
-        <v>4.2910492430259239E-2</v>
-      </c>
-      <c r="G51" s="55">
-        <f t="shared" si="21"/>
-        <v>20</v>
-      </c>
-      <c r="H51" s="56">
-        <f t="shared" si="22"/>
-        <v>49395</v>
-      </c>
-      <c r="I51" s="57">
-        <f t="shared" si="25"/>
-        <v>7140.5327272727254</v>
-      </c>
-      <c r="J51" s="58">
-        <f t="shared" si="27"/>
-        <v>4.4938613305745667E-2</v>
       </c>
     </row>
   </sheetData>
@@ -41616,8 +43058,8 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="L6:O6"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="B25:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="5.79" top="0.63" bottom="0.52" header="0.39" footer="0.73"/>
   <pageSetup paperSize="58" orientation="landscape" r:id="rId1"/>
@@ -41706,21 +43148,21 @@
       <c r="J6" s="71"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="218" t="s">
         <v>337</v>
       </c>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="218"/>
       <c r="E7" s="71"/>
-      <c r="F7" s="217" t="s">
+      <c r="F7" s="219" t="s">
         <v>159</v>
       </c>
-      <c r="G7" s="217"/>
+      <c r="G7" s="219"/>
       <c r="H7" s="71"/>
-      <c r="I7" s="217" t="s">
+      <c r="I7" s="219" t="s">
         <v>160</v>
       </c>
-      <c r="J7" s="217"/>
+      <c r="J7" s="219"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="71"/>
